--- a/data/dividends_info_20260613.xlsx
+++ b/data/dividends_info_20260613.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4392,11 +4392,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.24</v>
+        <v>0.85</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4420,14 +4420,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>IT0004967292</t>
+          <t>IT0005246191</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>9.180000305175781</v>
+        <v>49.5</v>
       </c>
       <c r="I85" t="n">
-        <v>2.614378998056083</v>
+        <v>1.717171717171717</v>
       </c>
       <c r="J85" t="n">
         <v>-26</v>
@@ -4439,11 +4439,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4467,14 +4467,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>IT0000072170</t>
+          <t>IT0003115950</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>21.93000030517578</v>
+        <v>37.29999923706055</v>
       </c>
       <c r="I86" t="n">
-        <v>3.6023711309003</v>
+        <v>2.278820421946435</v>
       </c>
       <c r="J86" t="n">
         <v>-26</v>
@@ -4486,11 +4486,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.093</v>
+        <v>1.3</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4514,14 +4514,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>IT0005345233</t>
+          <t>IT0003492391</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.360000133514404</v>
+        <v>66.5</v>
       </c>
       <c r="I87" t="n">
-        <v>1.735074583645998</v>
+        <v>1.954887218045113</v>
       </c>
       <c r="J87" t="n">
         <v>-26</v>
@@ -4533,11 +4533,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.06</v>
+        <v>0.6</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4556,19 +4556,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>IT0005359101</t>
+          <t>IT0001463063</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>7.400000095367432</v>
+        <v>7.039999961853027</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8108108003614941</v>
+        <v>8.522727318908558</v>
       </c>
       <c r="J88" t="n">
         <v>-26</v>
@@ -4580,11 +4580,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>IT0001078911</t>
+          <t>IT0005669558</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>35</v>
+        <v>6.5</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>7.230769230769231</v>
       </c>
       <c r="J89" t="n">
         <v>-26</v>
@@ -4627,11 +4627,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5543</v>
+        <v>0.2</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4650,19 +4650,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>IT0005090300</t>
+          <t>IT0005312027</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>6.579999923706055</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="I90" t="n">
-        <v>8.424012255729656</v>
+        <v>3.514938453229105</v>
       </c>
       <c r="J90" t="n">
         <v>-26</v>
@@ -4674,11 +4674,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4702,14 +4702,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>IT0001077780</t>
+          <t>IT0001157020</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>2.240000009536743</v>
+        <v>24.05999946594238</v>
       </c>
       <c r="I91" t="n">
-        <v>2.678571417167479</v>
+        <v>4.156276068981334</v>
       </c>
       <c r="J91" t="n">
         <v>-26</v>
@@ -4721,11 +4721,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2</v>
+        <v>0.215</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4749,14 +4749,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>IT0003411417</t>
+          <t>IT0004356751</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>14.19999980926514</v>
+        <v>4.920000076293945</v>
       </c>
       <c r="I92" t="n">
-        <v>1.408450723143708</v>
+        <v>4.369918631423103</v>
       </c>
       <c r="J92" t="n">
         <v>-26</v>
@@ -4768,11 +4768,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.103</v>
+        <v>0.27</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4791,19 +4791,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>IT0005186371</t>
+          <t>IT0003132476</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>7.164999961853027</v>
+        <v>23.21999931335449</v>
       </c>
       <c r="I93" t="n">
-        <v>1.437543622447723</v>
+        <v>1.162790732059648</v>
       </c>
       <c r="J93" t="n">
         <v>-26</v>
@@ -4815,11 +4815,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IT0000072618</t>
+          <t>IT0005521247</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>5.840000152587891</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="I94" t="n">
-        <v>3.253424572528563</v>
+        <v>2.040816286810733</v>
       </c>
       <c r="J94" t="n">
         <v>-26</v>
@@ -4862,11 +4862,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.432</v>
+        <v>0.24</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>IT0005211237</t>
+          <t>IT0004967292</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>10.64999961853027</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I95" t="n">
-        <v>4.056338173461992</v>
+        <v>2.614378998056083</v>
       </c>
       <c r="J95" t="n">
         <v>-26</v>
@@ -4909,11 +4909,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.44</v>
+        <v>0.79</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>IT0005541336</t>
+          <t>IT0000072170</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>27.53000068664551</v>
+        <v>21.93000030517578</v>
       </c>
       <c r="I96" t="n">
-        <v>1.598256407648544</v>
+        <v>3.6023711309003</v>
       </c>
       <c r="J96" t="n">
         <v>-26</v>
@@ -4956,11 +4956,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.03</v>
+        <v>0.093</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4984,14 +4984,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>IT0004522162</t>
+          <t>IT0005345233</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1.039999961853027</v>
+        <v>5.360000133514404</v>
       </c>
       <c r="I97" t="n">
-        <v>2.88461549042245</v>
+        <v>1.735074583645998</v>
       </c>
       <c r="J97" t="n">
         <v>-26</v>
@@ -5003,11 +5003,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.47</v>
+        <v>0.06</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5026,19 +5026,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>IT0003428445</t>
+          <t>IT0005359101</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>6.909999847412109</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I98" t="n">
-        <v>6.801736763800675</v>
+        <v>0.8108108003614941</v>
       </c>
       <c r="J98" t="n">
         <v>-26</v>
@@ -5050,11 +5050,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1.4</v>
+        <v>0.35</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5078,14 +5078,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0001078911</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>53.86000061035156</v>
+        <v>35</v>
       </c>
       <c r="I99" t="n">
-        <v>2.59933157098949</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>-26</v>
@@ -5097,11 +5097,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.3</v>
+        <v>0.5543</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>IT0005366767</t>
+          <t>IT0005090300</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>3.394999980926514</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="I100" t="n">
-        <v>8.836524350086398</v>
+        <v>8.424012255729656</v>
       </c>
       <c r="J100" t="n">
         <v>-26</v>
@@ -5144,11 +5144,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IT0005594418</t>
+          <t>IT0001077780</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>15.69999980926514</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I101" t="n">
-        <v>0.7643312194767268</v>
+        <v>2.678571417167479</v>
       </c>
       <c r="J101" t="n">
         <v>-26</v>
@@ -5191,11 +5191,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IT0005453748</t>
+          <t>IT0003411417</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>3.299999952316284</v>
+        <v>14.19999980926514</v>
       </c>
       <c r="I102" t="n">
-        <v>5.151515225952543</v>
+        <v>1.408450723143708</v>
       </c>
       <c r="J102" t="n">
         <v>-26</v>
@@ -5238,11 +5238,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7</v>
+        <v>0.103</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IT0005373789</t>
+          <t>IT0005186371</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>22.64999961853027</v>
+        <v>7.164999961853027</v>
       </c>
       <c r="I103" t="n">
-        <v>3.090507778319433</v>
+        <v>1.437543622447723</v>
       </c>
       <c r="J103" t="n">
         <v>-26</v>
@@ -5285,11 +5285,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.035</v>
+        <v>0.19</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IT0005378143</t>
+          <t>IT0000072618</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>2.859999895095825</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I104" t="n">
-        <v>1.22377626866407</v>
+        <v>3.253424572528563</v>
       </c>
       <c r="J104" t="n">
         <v>-26</v>
@@ -5332,11 +5332,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.33</v>
+        <v>0.432</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>IT0005054967</t>
+          <t>IT0005211237</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>5.610000133514404</v>
+        <v>10.64999961853027</v>
       </c>
       <c r="I105" t="n">
-        <v>5.882352801180245</v>
+        <v>4.056338173461992</v>
       </c>
       <c r="J105" t="n">
         <v>-26</v>
@@ -5379,11 +5379,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5407,14 +5407,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>IT0004931496</t>
+          <t>IT0005541336</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>0.9430000185966492</v>
+        <v>27.53000068664551</v>
       </c>
       <c r="I106" t="n">
-        <v>7.423117563048661</v>
+        <v>1.598256407648544</v>
       </c>
       <c r="J106" t="n">
         <v>-26</v>
@@ -5426,11 +5426,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.71</v>
+        <v>0.03</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>IT0003828271</t>
+          <t>IT0004522162</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>50.79999923706055</v>
+        <v>1.039999961853027</v>
       </c>
       <c r="I107" t="n">
-        <v>1.397637816266004</v>
+        <v>2.88461549042245</v>
       </c>
       <c r="J107" t="n">
         <v>-26</v>
@@ -5473,11 +5473,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1.35</v>
+        <v>0.47</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IT0005282865</t>
+          <t>IT0003428445</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>100.1999969482422</v>
+        <v>6.909999847412109</v>
       </c>
       <c r="I108" t="n">
-        <v>1.347305430255987</v>
+        <v>6.801736763800675</v>
       </c>
       <c r="J108" t="n">
         <v>-26</v>
@@ -5520,11 +5520,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.08</v>
+        <v>1.4</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IT0005543613</t>
+          <t>IT0004965148</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>7.320000171661377</v>
+        <v>53.86000061035156</v>
       </c>
       <c r="I109" t="n">
-        <v>1.092896149233872</v>
+        <v>2.59933157098949</v>
       </c>
       <c r="J109" t="n">
         <v>-26</v>
@@ -5567,11 +5567,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5595,14 +5595,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>IT0001017851</t>
+          <t>IT0005366767</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>254</v>
+        <v>3.394999980926514</v>
       </c>
       <c r="I110" t="n">
-        <v>1.181102362204724</v>
+        <v>8.836524350086398</v>
       </c>
       <c r="J110" t="n">
         <v>-26</v>
@@ -5614,11 +5614,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5642,14 +5642,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>IT0005495657</t>
+          <t>IT0005594418</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>4.71999979019165</v>
+        <v>15.69999980926514</v>
       </c>
       <c r="I111" t="n">
-        <v>3.601695075352903</v>
+        <v>0.7643312194767268</v>
       </c>
       <c r="J111" t="n">
         <v>-26</v>
@@ -5661,11 +5661,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.297</v>
+        <v>0.17</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0005568461</t>
+          <t>IT0005453748</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>7.400000095367432</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I112" t="n">
-        <v>4.013513461789396</v>
+        <v>5.151515225952543</v>
       </c>
       <c r="J112" t="n">
         <v>-26</v>
@@ -5708,11 +5708,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.45</v>
+        <v>0.7</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0001206769</t>
+          <t>IT0005373789</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>61</v>
+        <v>22.64999961853027</v>
       </c>
       <c r="I113" t="n">
-        <v>0.7377049180327869</v>
+        <v>3.090507778319433</v>
       </c>
       <c r="J113" t="n">
         <v>-26</v>
@@ -5755,11 +5755,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.04</v>
+        <v>0.035</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5783,14 +5783,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0005595423</t>
+          <t>IT0005378143</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>5.639999866485596</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="I114" t="n">
-        <v>0.709219874945225</v>
+        <v>1.22377626866407</v>
       </c>
       <c r="J114" t="n">
         <v>-26</v>
@@ -5802,11 +5802,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1.05</v>
+        <v>0.33</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0003549422</t>
+          <t>IT0005054967</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>37.2599983215332</v>
+        <v>5.610000133514404</v>
       </c>
       <c r="I115" t="n">
-        <v>2.818035553676305</v>
+        <v>5.882352801180245</v>
       </c>
       <c r="J115" t="n">
         <v>-26</v>
@@ -5849,11 +5849,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0005621070</t>
+          <t>IT0004931496</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1.549999952316284</v>
+        <v>0.9430000185966492</v>
       </c>
       <c r="I116" t="n">
-        <v>3.225806550850609</v>
+        <v>7.423117563048661</v>
       </c>
       <c r="J116" t="n">
         <v>-26</v>
@@ -5896,11 +5896,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>IT0005162406</t>
+          <t>IT0003828271</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>16.80999946594238</v>
+        <v>50.79999923706055</v>
       </c>
       <c r="I117" t="n">
-        <v>2.260559262776258</v>
+        <v>1.397637816266004</v>
       </c>
       <c r="J117" t="n">
         <v>-26</v>
@@ -5943,15 +5943,15 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6</v>
+        <v>1.35</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5971,14 +5971,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>LU2598331598</t>
+          <t>IT0005282865</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>27.1200008392334</v>
+        <v>100.1999969482422</v>
       </c>
       <c r="I118" t="n">
-        <v>2.212389312068178</v>
+        <v>1.347305430255987</v>
       </c>
       <c r="J118" t="n">
         <v>-26</v>
@@ -5990,11 +5990,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.35</v>
+        <v>0.08</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6018,14 +6018,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>IT0001454435</t>
+          <t>IT0005543613</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>36.84999847412109</v>
+        <v>7.320000171661377</v>
       </c>
       <c r="I119" t="n">
-        <v>0.9497965115135539</v>
+        <v>1.092896149233872</v>
       </c>
       <c r="J119" t="n">
         <v>-26</v>
@@ -6037,11 +6037,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.017</v>
+        <v>3</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6065,14 +6065,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>IT0005658841</t>
+          <t>IT0001017851</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>3.359999895095825</v>
+        <v>254</v>
       </c>
       <c r="I120" t="n">
-        <v>0.505952396748964</v>
+        <v>1.181102362204724</v>
       </c>
       <c r="J120" t="n">
         <v>-26</v>
@@ -6084,11 +6084,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6112,14 +6112,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>IT0005573065</t>
+          <t>IT0005495657</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>2.825000047683716</v>
+        <v>4.71999979019165</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3539822949100208</v>
+        <v>3.601695075352903</v>
       </c>
       <c r="J121" t="n">
         <v>-26</v>
@@ -6131,11 +6131,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.12</v>
+        <v>0.297</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6159,14 +6159,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IT0004810054</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>24.20000076293945</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I122" t="n">
-        <v>4.628099027646309</v>
+        <v>4.013513461789396</v>
       </c>
       <c r="J122" t="n">
         <v>-26</v>
@@ -6178,11 +6178,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6206,14 +6206,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>IT0004717200</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1.330000042915344</v>
+        <v>61</v>
       </c>
       <c r="I123" t="n">
-        <v>7.518796749870864</v>
+        <v>0.7377049180327869</v>
       </c>
       <c r="J123" t="n">
         <v>-26</v>
@@ -6225,11 +6225,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6253,14 +6253,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>IT0003865588</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>9.279999732971191</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="I124" t="n">
-        <v>2.801724218549686</v>
+        <v>0.709219874945225</v>
       </c>
       <c r="J124" t="n">
         <v>-26</v>
@@ -6272,11 +6272,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.09229999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6300,19 +6300,489 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>IT0005610958</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2.368000030517578</v>
+        <v>37.2599983215332</v>
       </c>
       <c r="I125" t="n">
-        <v>3.897804003821141</v>
+        <v>2.818035553676305</v>
       </c>
       <c r="J125" t="n">
         <v>-26</v>
       </c>
       <c r="K125" t="n">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Smart Capital S.p.A.</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>IT0005621070</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>1.549999952316284</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3.225806550850609</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TECHNOGYM S.p.A.</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>IT0005162406</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>16.80999946594238</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2.260559262776258</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TENARIS S.A.</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>DOLLARI USA</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>LU2598331598</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>27.1200008392334</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2.212389312068178</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>IT0001454435</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>36.84999847412109</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.9497965115135539</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Tecno S.p.A. Società Benefit</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>IT0005658841</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>3.359999895095825</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.505952396748964</v>
+      </c>
+      <c r="J130" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>UNIDATA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>IT0005573065</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>2.825000047683716</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3539822949100208</v>
+      </c>
+      <c r="J131" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K131" t="n">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Unipol S.p.A.</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>IT0004810054</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>24.20000076293945</v>
+      </c>
+      <c r="I132" t="n">
+        <v>4.628099027646309</v>
+      </c>
+      <c r="J132" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K132" t="n">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Vimi Fasteners S.p.A.</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>IT0004717200</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>1.330000042915344</v>
+      </c>
+      <c r="I133" t="n">
+        <v>7.518796749870864</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>WEBUILD S.p.A.</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>IT0003865588</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>9.279999732971191</v>
+      </c>
+      <c r="I134" t="n">
+        <v>2.801724218549686</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>doValue S.p.A.</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0.09229999999999999</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>EURO</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>IT0005610958</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>2.368000030517578</v>
+      </c>
+      <c r="I135" t="n">
+        <v>3.897804003821141</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K135" t="n">
         <v>-24</v>
       </c>
     </row>
